--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 12 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 13 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 13 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 14 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 15 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 16 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 16 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 17 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 17 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 18 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 18 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 19 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 19 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 20 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 20 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 21 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 21 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 22 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 22 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 23 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 23 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 24 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 24 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 25 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 25 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 26 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 26 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 27 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 27 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 28 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 28 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 29 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 29 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 30 September 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 30 September 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 1 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 1 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 2 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 2 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 3 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 3 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 4 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 4 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 5 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 5 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 6 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 6 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 7 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 7 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 8 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 8 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 9 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 9 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 10 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 10 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 11 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 11 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 12 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 12 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 13 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 13 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 14 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 14 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 15 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 15 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 16 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 16 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 17 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 17 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 18 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 18 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 19 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 20 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 21 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 21 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 22 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 22 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 23 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 23 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 24 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 24 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 25 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 25 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 26 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 26 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 27 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 27 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 28 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 28 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 29 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 29 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 30 October 2026]
 </t>
   </si>
   <si>

--- a/data/nomis_latest.xlsx
+++ b/data/nomis_latest.xlsx
@@ -228,7 +228,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 30 October 2026]
+    <t xml:space="preserve">ONS Crown Copyright Reserved [from Nomis on 31 October 2026]
 </t>
   </si>
   <si>
